--- a/5/search/FY5_Missile3_results/fine_tuned/comparison.xlsx
+++ b/5/search/FY5_Missile3_results/fine_tuned/comparison.xlsx
@@ -489,16 +489,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>116.2</v>
+        <v>117</v>
       </c>
       <c r="C3" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D3" t="n">
-        <v>12.2</v>
+        <v>12</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8</v>
+        <v>0.8999999999999999</v>
       </c>
       <c r="F3" t="n">
         <v>3.800000000000001</v>
